--- a/sources/3C_Manha_2_Bimestre.xlsx
+++ b/sources/3C_Manha_2_Bimestre.xlsx
@@ -61,7 +61,7 @@
     <x:t>Conselho Segundo Bimestre</x:t>
   </x:si>
   <x:si>
-    <x:t>214</x:t>
+    <x:t>318</x:t>
   </x:si>
   <x:si>
     <x:t>0 (Soma de todas as eletivas)</x:t>
@@ -179,16 +179,22 @@
     <x:t>9</x:t>
   </x:si>
   <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
     <x:t>-</x:t>
   </x:si>
   <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85%</x:t>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83%</x:t>
   </x:si>
   <x:si>
     <x:t>ANDRE VITO LOPES</x:t>
@@ -197,21 +203,21 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
+    <x:t>98%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIANCA EGEA ARAUJO DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100%</x:t>
+  </x:si>
+  <x:si>
     <x:t>99%</x:t>
   </x:si>
   <x:si>
-    <x:t>98%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIANCA EGEA ARAUJO DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100%</x:t>
-  </x:si>
-  <x:si>
     <x:t>CAIQUE DOS SANTOS SOTTO</x:t>
   </x:si>
   <x:si>
@@ -230,189 +236,198 @@
     <x:t>17</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>66%</x:t>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CESAR AUGUSTO VIEIRA BRITO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>75%</x:t>
   </x:si>
   <x:si>
-    <x:t>CESAR AUGUSTO VIEIRA BRITO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
+    <x:t>77%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DANIEL MESAQUE ALAUK DA CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DANIEL SOUZA GONZAGA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAVID FERRAZ FROTA AFONSO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMERSON LEANDRO RAMOS RODRIGUES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FABIANO LIMA DO NASCIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLYPE OTTO NUNES LUCENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL CARDOSO MIRANDA DA CUNHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL SILVA OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUSTAVO NASCIMENTO MARQUES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Baixa - Transferência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERLAN SATURNINO BAZAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IGOR FERREIRA BASTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISABELLA ARCHAPA NASCIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JHULIAN ESTIF MAITA MAMANI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOAO VICTOR PEREIRA BRITO DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOAO VITOR MACHADO GOMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATHARINA SERTORIO CASTILHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAUA CECCONI FARINA DE SOUSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KEVIN BRYAN VELASQUEZ BALBOA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LARISSA VITORIA RIBEIRO SOUSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEONEL RONALDO COPA RAMOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Transferido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUIZ GUSTAVO AMORIM CAETANO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAICOLN LIMA DE FREITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIA CLARA FIGUEIREDO LIMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATHEUS BRUM SANTOS DE ALVARENGA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATHEUS CARDOSO DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATHEUS PEREIRA SALES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEL CALDEIRA SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEDRO HENRIQUE BRITO VILARINDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEDRO HENRIQUE DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYETRO ALCANTARA DE LIMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAQUEL QUERIN APUQUE ZANIN ROQUE</x:t>
   </x:si>
   <x:si>
     <x:t>78%</x:t>
   </x:si>
   <x:si>
-    <x:t>DANIEL MESAQUE ALAUK DA CRUZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAVID FERRAZ FROTA AFONSO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>97%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMERSON LEANDRO RAMOS RODRIGUES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FABIANO LIMA DO NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLYPE OTTO NUNES LUCENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIEL CARDOSO MIRANDA DA CUNHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIEL SILVA OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUSTAVO NASCIMENTO MARQUES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Baixa - Transferência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IGOR FERREIRA BASTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISABELLA ARCHAPA NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JHULIAN ESTIF MAITA MAMANI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOAO VICTOR PEREIRA BRITO DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>76%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOAO VITOR MACHADO GOMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATHARINA SERTORIO CASTILHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAUA CECCONI FARINA DE SOUSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KEVIN BRYAN VELASQUEZ BALBOA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LARISSA VITORIA RIBEIRO SOUSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEONEL RONALDO COPA RAMOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Transferido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUIZ GUSTAVO AMORIM CAETANO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAICOLN LIMA DE FREITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA CLARA FIGUEIREDO LIMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>53%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATHEUS BRUM SANTOS DE ALVARENGA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATHEUS CARDOSO DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>92%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATHEUS PEREIRA SALES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEL CALDEIRA SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEDRO HENRIQUE BRITO VILARINDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEDRO HENRIQUE DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYETRO ALCANTARA DE LIMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAQUEL QUERIN APUQUE ZANIN ROQUE</x:t>
-  </x:si>
-  <x:si>
     <x:t>ROGERIO DIAS NASCIMENTO FILHO</x:t>
   </x:si>
   <x:si>
@@ -425,6 +440,9 @@
     <x:t>Remanejamento</x:t>
   </x:si>
   <x:si>
+    <x:t>89%</x:t>
+  </x:si>
+  <x:si>
     <x:t>WEVERTON CLEITON APARECIDO DOS REIS FERREIRA</x:t>
   </x:si>
   <x:si>
@@ -434,15 +452,6 @@
     <x:t>YUMI EUGENIO URATA</x:t>
   </x:si>
   <x:si>
-    <x:t>DANIEL SOUZA GONZAGA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERLAN SATURNINO BAZAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>63%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve"> </x:t>
   </x:si>
   <x:si>
@@ -458,10 +467,13 @@
     <x:t>Aulas Dadas: 30</x:t>
   </x:si>
   <x:si>
-    <x:t>Aulas Dadas: 0</x:t>
+    <x:t>Aulas Dadas: 38</x:t>
   </x:si>
   <x:si>
     <x:t>Aulas Dadas: 27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aulas Dadas: 28</x:t>
   </x:si>
   <x:si>
     <x:t>Legenda</x:t>
@@ -1376,13 +1388,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U13" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="V13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W13" s="12">
         <x:v>1</x:v>
@@ -1391,7 +1403,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Y13" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z13" s="12" t="s">
         <x:v>46</x:v>
@@ -1403,7 +1415,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD13" s="12" t="s">
         <x:v>46</x:v>
@@ -1412,22 +1424,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AF13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AJ13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL13" s="12" t="s">
         <x:v>46</x:v>
@@ -1436,30 +1448,30 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AP13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ13" s="12">
-        <x:v>33</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AR13" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS13" s="12">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="AT13" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:46">
       <x:c r="A14" s="11" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="12" t="s">
         <x:v>43</x:v>
@@ -1480,10 +1492,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J14" s="12" t="s">
         <x:v>46</x:v>
@@ -1507,22 +1519,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="Q14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="S14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="T14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W14" s="12">
         <x:v>2</x:v>
@@ -1531,7 +1543,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Y14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z14" s="12" t="s">
         <x:v>46</x:v>
@@ -1552,19 +1564,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AF14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AJ14" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK14" s="12" t="s">
         <x:v>46</x:v>
@@ -1576,30 +1588,30 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AN14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ14" s="12">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AR14" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS14" s="12">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AT14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:46">
       <x:c r="A15" s="11" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B15" s="12" t="s">
         <x:v>43</x:v>
@@ -1656,19 +1668,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="X15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Y15" s="12" t="s">
         <x:v>46</x:v>
@@ -1680,7 +1692,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AB15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AC15" s="12" t="s">
         <x:v>46</x:v>
@@ -1692,13 +1704,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AF15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI15" s="12">
         <x:v>3</x:v>
@@ -1716,30 +1728,30 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AN15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AO15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ15" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AR15" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AT15" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:46">
       <x:c r="A16" s="11" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
         <x:v>43</x:v>
@@ -1796,13 +1808,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="T16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W16" s="12">
         <x:v>4</x:v>
@@ -1832,13 +1844,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AF16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI16" s="12">
         <x:v>4</x:v>
@@ -1856,30 +1868,30 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AN16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ16" s="12">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="AR16" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AS16" s="12">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="AT16" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:46">
       <x:c r="A17" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
         <x:v>43</x:v>
@@ -1891,7 +1903,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
         <x:v>46</x:v>
@@ -1900,10 +1912,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I17" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J17" s="12" t="s">
         <x:v>46</x:v>
@@ -1912,10 +1924,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M17" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="N17" s="12" t="s">
         <x:v>46</x:v>
@@ -1924,25 +1936,25 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="P17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q17" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="R17" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="S17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="T17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="V17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W17" s="12">
         <x:v>5</x:v>
@@ -1972,22 +1984,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AF17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AH17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AJ17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK17" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL17" s="12" t="s">
         <x:v>46</x:v>
@@ -1996,30 +2008,30 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AN17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AP17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ17" s="12">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="AR17" s="12" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="AS17" s="12">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="AT17" s="12" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="AR17" s="12" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="AS17" s="12">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="AT17" s="12" t="s">
-        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:46">
       <x:c r="A18" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
         <x:v>43</x:v>
@@ -2031,7 +2043,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F18" s="12" t="s">
         <x:v>47</x:v>
@@ -2040,7 +2052,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I18" s="12" t="s">
         <x:v>50</x:v>
@@ -2052,7 +2064,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M18" s="12" t="s">
         <x:v>47</x:v>
@@ -2067,22 +2079,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="Q18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R18" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="S18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="T18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="V18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W18" s="12">
         <x:v>6</x:v>
@@ -2091,7 +2103,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Y18" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Z18" s="12" t="s">
         <x:v>46</x:v>
@@ -2112,22 +2124,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AF18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AH18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AJ18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL18" s="12" t="s">
         <x:v>46</x:v>
@@ -2136,30 +2148,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AN18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AO18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AP18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ18" s="12">
-        <x:v>48</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AR18" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="AS18" s="12">
-        <x:v>98</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="AT18" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:46">
       <x:c r="A19" s="11" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B19" s="12" t="s">
         <x:v>43</x:v>
@@ -2180,7 +2192,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="H19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I19" s="12" t="s">
         <x:v>75</x:v>
@@ -2204,13 +2216,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="P19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q19" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="R19" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="S19" s="12">
         <x:v>7</x:v>
@@ -2219,10 +2231,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="U19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W19" s="12">
         <x:v>7</x:v>
@@ -2252,19 +2264,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AF19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AH19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AJ19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK19" s="12" t="s">
         <x:v>47</x:v>
@@ -2276,30 +2288,30 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AN19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AP19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ19" s="12">
-        <x:v>49</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AR19" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AS19" s="12">
-        <x:v>73</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="AT19" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:46">
       <x:c r="A20" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
         <x:v>43</x:v>
@@ -2308,10 +2320,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F20" s="12" t="s">
         <x:v>46</x:v>
@@ -2320,10 +2332,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I20" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J20" s="12" t="s">
         <x:v>46</x:v>
@@ -2332,10 +2344,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L20" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M20" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="N20" s="12" t="s">
         <x:v>46</x:v>
@@ -2344,34 +2356,34 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="P20" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R20" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="S20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="T20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="X20" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z20" s="12" t="s">
         <x:v>46</x:v>
@@ -2383,7 +2395,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD20" s="12" t="s">
         <x:v>46</x:v>
@@ -2392,22 +2404,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AF20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AH20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AJ20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL20" s="12" t="s">
         <x:v>46</x:v>
@@ -2416,30 +2428,30 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AN20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AP20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ20" s="12">
-        <x:v>13</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AR20" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AS20" s="12">
-        <x:v>15</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="AT20" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:46">
       <x:c r="A21" s="11" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
         <x:v>43</x:v>
@@ -2448,10 +2460,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F21" s="12" t="s">
         <x:v>46</x:v>
@@ -2460,10 +2472,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J21" s="12" t="s">
         <x:v>46</x:v>
@@ -2472,10 +2484,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N21" s="12" t="s">
         <x:v>46</x:v>
@@ -2484,34 +2496,34 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="P21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Q21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="S21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="T21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="X21" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Y21" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z21" s="12" t="s">
         <x:v>46</x:v>
@@ -2520,7 +2532,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AB21" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="s">
         <x:v>45</x:v>
@@ -2532,13 +2544,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AF21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG21" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="AH21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI21" s="12">
         <x:v>9</x:v>
@@ -2547,7 +2559,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AK21" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL21" s="12" t="s">
         <x:v>46</x:v>
@@ -2556,30 +2568,30 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AN21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ21" s="12">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AR21" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AS21" s="12">
-        <x:v>52</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AT21" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:46">
       <x:c r="A22" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
         <x:v>43</x:v>
@@ -2588,10 +2600,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
         <x:v>46</x:v>
@@ -2600,10 +2612,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I22" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J22" s="12" t="s">
         <x:v>46</x:v>
@@ -2612,10 +2624,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L22" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N22" s="12" t="s">
         <x:v>46</x:v>
@@ -2624,25 +2636,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="P22" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q22" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="S22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="T22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="U22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W22" s="12">
         <x:v>10</x:v>
@@ -2651,7 +2663,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Y22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z22" s="12" t="s">
         <x:v>46</x:v>
@@ -2663,7 +2675,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD22" s="12" t="s">
         <x:v>46</x:v>
@@ -2672,22 +2684,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AF22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AH22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AJ22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AL22" s="12" t="s">
         <x:v>46</x:v>
@@ -2696,30 +2708,30 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AN22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AO22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AP22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ22" s="12">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AR22" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AS22" s="12">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AT22" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:46">
       <x:c r="A23" s="11" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
         <x:v>43</x:v>
@@ -2728,22 +2740,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="H23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I23" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J23" s="12" t="s">
         <x:v>46</x:v>
@@ -2752,10 +2764,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="L23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N23" s="12" t="s">
         <x:v>46</x:v>
@@ -2764,34 +2776,34 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="P23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q23" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R23" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="T23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U23" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="V23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="X23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y23" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z23" s="12" t="s">
         <x:v>46</x:v>
@@ -2800,10 +2812,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AB23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC23" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD23" s="12" t="s">
         <x:v>46</x:v>
@@ -2812,22 +2824,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AF23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AJ23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL23" s="12" t="s">
         <x:v>46</x:v>
@@ -2836,30 +2848,30 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AN23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AO23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ23" s="12">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="AR23" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="AS23" s="12">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AT23" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:46">
       <x:c r="A24" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
         <x:v>43</x:v>
@@ -2868,22 +2880,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="H24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I24" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J24" s="12" t="s">
         <x:v>46</x:v>
@@ -2892,10 +2904,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="L24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N24" s="12" t="s">
         <x:v>46</x:v>
@@ -2904,34 +2916,34 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="P24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q24" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="R24" s="12" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="R24" s="12" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="S24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="T24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="X24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y24" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z24" s="12" t="s">
         <x:v>46</x:v>
@@ -2940,10 +2952,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AB24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC24" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD24" s="12" t="s">
         <x:v>46</x:v>
@@ -2952,22 +2964,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AF24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG24" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="AH24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="AJ24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL24" s="12" t="s">
         <x:v>46</x:v>
@@ -2976,22 +2988,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AN24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ24" s="12">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AS24" s="12">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AT24" s="12" t="s">
         <x:v>91</x:v>
@@ -3008,10 +3020,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F25" s="12" t="s">
         <x:v>46</x:v>
@@ -3020,10 +3032,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H25" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J25" s="12" t="s">
         <x:v>46</x:v>
@@ -3044,34 +3056,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="P25" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="Q25" s="12" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="Q25" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="R25" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="S25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="T25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="X25" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Y25" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z25" s="12" t="s">
         <x:v>46</x:v>
@@ -3080,10 +3092,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AB25" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AC25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD25" s="12" t="s">
         <x:v>46</x:v>
@@ -3092,22 +3104,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AF25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AH25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="AJ25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL25" s="12" t="s">
         <x:v>46</x:v>
@@ -3116,25 +3128,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AN25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ25" s="12">
-        <x:v>19</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AR25" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="AS25" s="12">
-        <x:v>29</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="AT25" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:46">
@@ -3142,16 +3154,16 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F26" s="12" t="s">
         <x:v>46</x:v>
@@ -3160,10 +3172,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I26" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J26" s="12" t="s">
         <x:v>46</x:v>
@@ -3172,10 +3184,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="L26" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M26" s="12" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="M26" s="12" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="N26" s="12" t="s">
         <x:v>46</x:v>
@@ -3184,31 +3196,31 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="P26" s="12" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="Q26" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="R26" s="12" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="Q26" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="R26" s="12" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="S26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="T26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U26" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="V26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="X26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Y26" s="12" t="s">
         <x:v>46</x:v>
@@ -3220,10 +3232,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AB26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AC26" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD26" s="12" t="s">
         <x:v>46</x:v>
@@ -3232,22 +3244,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AF26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AJ26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK26" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL26" s="12" t="s">
         <x:v>46</x:v>
@@ -3256,42 +3268,42 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AN26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO26" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="AP26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ26" s="12">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="AR26" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="AS26" s="12">
-        <x:v>64</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="AT26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:46">
       <x:c r="A27" s="11" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E27" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F27" s="12" t="s">
         <x:v>46</x:v>
@@ -3300,10 +3312,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
         <x:v>46</x:v>
@@ -3312,10 +3324,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M27" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N27" s="12" t="s">
         <x:v>46</x:v>
@@ -3324,34 +3336,34 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="P27" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q27" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="R27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="T27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z27" s="12" t="s">
         <x:v>46</x:v>
@@ -3360,10 +3372,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="s">
         <x:v>46</x:v>
@@ -3372,22 +3384,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AF27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AJ27" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
         <x:v>46</x:v>
@@ -3396,33 +3408,33 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ27" s="12">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS27" s="12">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AT27" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:46">
       <x:c r="A28" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C28" s="12">
         <x:v>16</x:v>
@@ -3431,7 +3443,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F28" s="12" t="s">
         <x:v>46</x:v>
@@ -3440,10 +3452,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J28" s="12" t="s">
         <x:v>46</x:v>
@@ -3452,10 +3464,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="L28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M28" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="N28" s="12" t="s">
         <x:v>46</x:v>
@@ -3464,25 +3476,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="P28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q28" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R28" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="S28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="T28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="V28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W28" s="12">
         <x:v>16</x:v>
@@ -3491,7 +3503,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="Y28" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z28" s="12" t="s">
         <x:v>46</x:v>
@@ -3503,7 +3515,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AC28" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AD28" s="12" t="s">
         <x:v>46</x:v>
@@ -3512,22 +3524,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AF28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AH28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AJ28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK28" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL28" s="12" t="s">
         <x:v>46</x:v>
@@ -3536,30 +3548,30 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AN28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ28" s="12">
-        <x:v>0</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="AR28" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AS28" s="12">
-        <x:v>22</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="AT28" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:46">
       <x:c r="A29" s="11" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
         <x:v>43</x:v>
@@ -3568,7 +3580,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
         <x:v>45</x:v>
@@ -3580,10 +3592,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J29" s="12" t="s">
         <x:v>46</x:v>
@@ -3592,10 +3604,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="L29" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N29" s="12" t="s">
         <x:v>46</x:v>
@@ -3604,34 +3616,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="R29" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="S29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
         <x:v>46</x:v>
@@ -3640,10 +3652,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AB29" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD29" s="12" t="s">
         <x:v>46</x:v>
@@ -3652,22 +3664,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
         <x:v>46</x:v>
@@ -3676,42 +3688,42 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AN29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ29" s="12">
-        <x:v>6</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AS29" s="12">
-        <x:v>19</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:46">
       <x:c r="A30" s="11" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F30" s="12" t="s">
         <x:v>46</x:v>
@@ -3720,10 +3732,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J30" s="12" t="s">
         <x:v>46</x:v>
@@ -3735,7 +3747,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M30" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N30" s="12" t="s">
         <x:v>46</x:v>
@@ -3744,34 +3756,34 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="P30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q30" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R30" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="T30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="X30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y30" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z30" s="12" t="s">
         <x:v>46</x:v>
@@ -3780,10 +3792,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AB30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC30" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD30" s="12" t="s">
         <x:v>46</x:v>
@@ -3792,13 +3804,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AF30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI30" s="12">
         <x:v>18</x:v>
@@ -3807,7 +3819,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
         <x:v>46</x:v>
@@ -3816,30 +3828,30 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AN30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ30" s="12">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR30" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="AR30" s="12" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="AS30" s="12">
-        <x:v>110</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="AT30" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:46">
       <x:c r="A31" s="11" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
         <x:v>43</x:v>
@@ -3848,7 +3860,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
         <x:v>45</x:v>
@@ -3860,10 +3872,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J31" s="12" t="s">
         <x:v>46</x:v>
@@ -3872,10 +3884,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="L31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N31" s="12" t="s">
         <x:v>46</x:v>
@@ -3884,34 +3896,34 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R31" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="T31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="X31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z31" s="12" t="s">
         <x:v>46</x:v>
@@ -3920,10 +3932,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AB31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD31" s="12" t="s">
         <x:v>46</x:v>
@@ -3932,22 +3944,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
         <x:v>46</x:v>
@@ -3956,30 +3968,30 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AN31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ31" s="12">
-        <x:v>52</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AS31" s="12">
-        <x:v>63</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="AT31" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:46">
       <x:c r="A32" s="11" t="s">
-        <x:v>103</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>43</x:v>
@@ -3988,10 +4000,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F32" s="12" t="s">
         <x:v>46</x:v>
@@ -4000,10 +4012,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I32" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J32" s="12" t="s">
         <x:v>46</x:v>
@@ -4012,10 +4024,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N32" s="12" t="s">
         <x:v>46</x:v>
@@ -4024,34 +4036,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Q32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="R32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="S32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="V32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="X32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Z32" s="12" t="s">
         <x:v>46</x:v>
@@ -4060,10 +4072,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="s">
         <x:v>46</x:v>
@@ -4072,22 +4084,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AF32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
         <x:v>46</x:v>
@@ -4096,30 +4108,30 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AN32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ32" s="12">
-        <x:v>42</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>104</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="AS32" s="12">
-        <x:v>63</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="AT32" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:46">
       <x:c r="A33" s="11" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
         <x:v>43</x:v>
@@ -4128,7 +4140,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
         <x:v>45</x:v>
@@ -4140,10 +4152,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J33" s="12" t="s">
         <x:v>46</x:v>
@@ -4152,10 +4164,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="L33" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N33" s="12" t="s">
         <x:v>46</x:v>
@@ -4164,10 +4176,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="P33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="R33" s="12" t="s">
         <x:v>68</x:v>
@@ -4176,22 +4188,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="X33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z33" s="12" t="s">
         <x:v>46</x:v>
@@ -4200,10 +4212,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AD33" s="12" t="s">
         <x:v>46</x:v>
@@ -4212,22 +4224,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AF33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AH33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="AJ33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
         <x:v>46</x:v>
@@ -4236,30 +4248,30 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AN33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ33" s="12">
-        <x:v>54</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AS33" s="12">
-        <x:v>70</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AT33" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:46">
       <x:c r="A34" s="11" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
         <x:v>43</x:v>
@@ -4268,10 +4280,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
         <x:v>46</x:v>
@@ -4280,10 +4292,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J34" s="12" t="s">
         <x:v>46</x:v>
@@ -4292,10 +4304,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="L34" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
         <x:v>46</x:v>
@@ -4304,34 +4316,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="P34" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R34" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="S34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="T34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="X34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z34" s="12" t="s">
         <x:v>46</x:v>
@@ -4340,10 +4352,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AB34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD34" s="12" t="s">
         <x:v>46</x:v>
@@ -4352,22 +4364,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AF34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AH34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="AJ34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
         <x:v>46</x:v>
@@ -4376,30 +4388,30 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AN34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AO34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ34" s="12">
-        <x:v>0</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="AS34" s="12">
-        <x:v>0</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:46">
       <x:c r="A35" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
         <x:v>43</x:v>
@@ -4408,10 +4420,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
         <x:v>46</x:v>
@@ -4420,10 +4432,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H35" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J35" s="12" t="s">
         <x:v>46</x:v>
@@ -4432,10 +4444,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N35" s="12" t="s">
         <x:v>46</x:v>
@@ -4444,34 +4456,34 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Q35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="S35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="T35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="V35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="X35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y35" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Z35" s="12" t="s">
         <x:v>46</x:v>
@@ -4480,10 +4492,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AB35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC35" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD35" s="12" t="s">
         <x:v>46</x:v>
@@ -4492,22 +4504,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AF35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AH35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="AJ35" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL35" s="12" t="s">
         <x:v>46</x:v>
@@ -4516,39 +4528,39 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AN35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ35" s="12">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="AR35" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="AS35" s="12">
-        <x:v>23</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AT35" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:46">
       <x:c r="A36" s="11" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
         <x:v>46</x:v>
@@ -4560,7 +4572,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I36" s="12" t="s">
         <x:v>46</x:v>
@@ -4572,7 +4584,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="L36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M36" s="12" t="s">
         <x:v>46</x:v>
@@ -4584,31 +4596,31 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="P36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Q36" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="R36" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="T36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="X36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y36" s="12" t="s">
         <x:v>46</x:v>
@@ -4620,7 +4632,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AB36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
         <x:v>46</x:v>
@@ -4632,19 +4644,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AF36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="AJ36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK36" s="12" t="s">
         <x:v>46</x:v>
@@ -4656,30 +4668,30 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AN36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ36" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AR36" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS36" s="12">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:46">
       <x:c r="A37" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
         <x:v>43</x:v>
@@ -4688,10 +4700,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
         <x:v>46</x:v>
@@ -4700,10 +4712,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J37" s="12" t="s">
         <x:v>46</x:v>
@@ -4712,10 +4724,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L37" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N37" s="12" t="s">
         <x:v>46</x:v>
@@ -4724,34 +4736,34 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="T37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U37" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="V37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z37" s="12" t="s">
         <x:v>46</x:v>
@@ -4760,10 +4772,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD37" s="12" t="s">
         <x:v>46</x:v>
@@ -4772,22 +4784,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AF37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AJ37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
         <x:v>46</x:v>
@@ -4796,39 +4808,39 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AN37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AO37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ37" s="12">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AS37" s="12">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:46">
       <x:c r="A38" s="11" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
         <x:v>46</x:v>
@@ -4840,7 +4852,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="H38" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
         <x:v>46</x:v>
@@ -4852,7 +4864,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="L38" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
         <x:v>46</x:v>
@@ -4864,7 +4876,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="P38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="s">
         <x:v>46</x:v>
@@ -4876,19 +4888,19 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="T38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
         <x:v>46</x:v>
@@ -4900,7 +4912,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
         <x:v>46</x:v>
@@ -4912,19 +4924,19 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AF38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="AJ38" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
         <x:v>46</x:v>
@@ -4936,30 +4948,30 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ38" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AR38" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS38" s="12">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:46">
       <x:c r="A39" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
         <x:v>43</x:v>
@@ -4968,10 +4980,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
         <x:v>46</x:v>
@@ -4980,10 +4992,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H39" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
         <x:v>46</x:v>
@@ -4992,10 +5004,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="L39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M39" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N39" s="12" t="s">
         <x:v>46</x:v>
@@ -5004,34 +5016,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="P39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q39" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="S39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="T39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z39" s="12" t="s">
         <x:v>46</x:v>
@@ -5040,10 +5052,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>46</x:v>
@@ -5052,22 +5064,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AF39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
         <x:v>46</x:v>
@@ -5076,30 +5088,30 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AN39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ39" s="12">
-        <x:v>123</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>116</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="AS39" s="12">
-        <x:v>210</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:46">
       <x:c r="A40" s="11" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
         <x:v>43</x:v>
@@ -5108,10 +5120,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
         <x:v>46</x:v>
@@ -5120,10 +5132,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
         <x:v>46</x:v>
@@ -5132,10 +5144,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="L40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N40" s="12" t="s">
         <x:v>46</x:v>
@@ -5147,22 +5159,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R40" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="T40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W40" s="12">
         <x:v>28</x:v>
@@ -5180,10 +5192,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AB40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
         <x:v>46</x:v>
@@ -5192,22 +5204,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AF40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="AJ40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
         <x:v>46</x:v>
@@ -5216,30 +5228,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AN40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ40" s="12">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR40" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS40" s="12">
-        <x:v>25</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:46">
       <x:c r="A41" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
         <x:v>43</x:v>
@@ -5248,10 +5260,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
         <x:v>46</x:v>
@@ -5260,10 +5272,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I41" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="J41" s="12" t="s">
         <x:v>46</x:v>
@@ -5272,10 +5284,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="L41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="N41" s="12" t="s">
         <x:v>46</x:v>
@@ -5284,34 +5296,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="P41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R41" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="T41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="V41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="X41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="Z41" s="12" t="s">
         <x:v>46</x:v>
@@ -5320,10 +5332,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AB41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>46</x:v>
@@ -5332,22 +5344,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AF41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="AJ41" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
         <x:v>46</x:v>
@@ -5356,30 +5368,30 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AN41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ41" s="12">
-        <x:v>17</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="AS41" s="12">
-        <x:v>15</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:46">
       <x:c r="A42" s="11" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
         <x:v>43</x:v>
@@ -5388,10 +5400,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F42" s="12" t="s">
         <x:v>46</x:v>
@@ -5400,10 +5412,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J42" s="12" t="s">
         <x:v>46</x:v>
@@ -5412,10 +5424,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L42" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N42" s="12" t="s">
         <x:v>46</x:v>
@@ -5427,28 +5439,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="S42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
         <x:v>46</x:v>
@@ -5460,10 +5472,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AB42" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="s">
         <x:v>46</x:v>
@@ -5472,22 +5484,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AF42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
         <x:v>46</x:v>
@@ -5496,30 +5508,30 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AN42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="AP42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ42" s="12">
-        <x:v>1</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AS42" s="12">
-        <x:v>1</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:46">
       <x:c r="A43" s="11" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
         <x:v>43</x:v>
@@ -5531,7 +5543,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F43" s="12" t="s">
         <x:v>46</x:v>
@@ -5552,10 +5564,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M43" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N43" s="12" t="s">
         <x:v>46</x:v>
@@ -5564,25 +5576,25 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="P43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="T43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W43" s="12">
         <x:v>31</x:v>
@@ -5591,7 +5603,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Y43" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z43" s="12" t="s">
         <x:v>46</x:v>
@@ -5603,7 +5615,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AD43" s="12" t="s">
         <x:v>46</x:v>
@@ -5612,22 +5624,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AF43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
         <x:v>46</x:v>
@@ -5636,30 +5648,30 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AN43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ43" s="12">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="AS43" s="12">
-        <x:v>3</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:46">
       <x:c r="A44" s="11" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
         <x:v>43</x:v>
@@ -5680,10 +5692,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H44" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
         <x:v>46</x:v>
@@ -5692,7 +5704,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="L44" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M44" s="12" t="s">
         <x:v>46</x:v>
@@ -5704,34 +5716,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="P44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q44" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R44" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="T44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="X44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Y44" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z44" s="12" t="s">
         <x:v>46</x:v>
@@ -5740,10 +5752,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AB44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
         <x:v>46</x:v>
@@ -5752,19 +5764,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AF44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="AJ44" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
         <x:v>46</x:v>
@@ -5776,30 +5788,30 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AN44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ44" s="12">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS44" s="12">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:46">
       <x:c r="A45" s="11" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
         <x:v>43</x:v>
@@ -5808,7 +5820,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
         <x:v>46</x:v>
@@ -5820,10 +5832,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
         <x:v>46</x:v>
@@ -5835,7 +5847,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N45" s="12" t="s">
         <x:v>46</x:v>
@@ -5847,31 +5859,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z45" s="12" t="s">
         <x:v>46</x:v>
@@ -5880,10 +5892,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="s">
         <x:v>46</x:v>
@@ -5892,13 +5904,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI45" s="12">
         <x:v>33</x:v>
@@ -5907,7 +5919,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
         <x:v>46</x:v>
@@ -5916,30 +5928,30 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ45" s="12">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AS45" s="12">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:46">
       <x:c r="A46" s="11" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
         <x:v>43</x:v>
@@ -5948,10 +5960,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="D46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F46" s="12" t="s">
         <x:v>46</x:v>
@@ -5960,10 +5972,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
         <x:v>46</x:v>
@@ -5975,7 +5987,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="M46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N46" s="12" t="s">
         <x:v>46</x:v>
@@ -5984,25 +5996,25 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="P46" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R46" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="T46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W46" s="12">
         <x:v>34</x:v>
@@ -6011,7 +6023,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Y46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z46" s="12" t="s">
         <x:v>46</x:v>
@@ -6023,7 +6035,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD46" s="12" t="s">
         <x:v>46</x:v>
@@ -6032,22 +6044,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AF46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AJ46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL46" s="12" t="s">
         <x:v>46</x:v>
@@ -6056,30 +6068,30 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AN46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ46" s="12">
-        <x:v>40</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AR46" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS46" s="12">
-        <x:v>77</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AT46" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:46">
       <x:c r="A47" s="11" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
         <x:v>43</x:v>
@@ -6088,10 +6100,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D47" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
         <x:v>46</x:v>
@@ -6100,10 +6112,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J47" s="12" t="s">
         <x:v>46</x:v>
@@ -6112,10 +6124,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L47" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
         <x:v>46</x:v>
@@ -6124,34 +6136,34 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R47" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="S47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="X47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Y47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
         <x:v>46</x:v>
@@ -6160,10 +6172,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
         <x:v>46</x:v>
@@ -6172,22 +6184,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AJ47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
         <x:v>46</x:v>
@@ -6196,42 +6208,42 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AN47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ47" s="12">
-        <x:v>48</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AS47" s="12">
-        <x:v>97</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:46">
       <x:c r="A48" s="11" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F48" s="12" t="s">
         <x:v>46</x:v>
@@ -6243,7 +6255,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
         <x:v>46</x:v>
@@ -6252,10 +6264,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="L48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N48" s="12" t="s">
         <x:v>46</x:v>
@@ -6264,34 +6276,34 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="P48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Q48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="S48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="T48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="V48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="X48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Z48" s="12" t="s">
         <x:v>46</x:v>
@@ -6300,10 +6312,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AC48" s="12" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="AC48" s="12" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="AD48" s="12" t="s">
         <x:v>46</x:v>
@@ -6312,22 +6324,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AJ48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
         <x:v>46</x:v>
@@ -6336,30 +6348,30 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ48" s="12">
-        <x:v>0</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="AS48" s="12">
-        <x:v>34</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:46">
       <x:c r="A49" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
         <x:v>43</x:v>
@@ -6368,10 +6380,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="D49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E49" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F49" s="12" t="s">
         <x:v>46</x:v>
@@ -6380,10 +6392,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J49" s="12" t="s">
         <x:v>46</x:v>
@@ -6395,7 +6407,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="M49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="N49" s="12" t="s">
         <x:v>46</x:v>
@@ -6404,34 +6416,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Q49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="R49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="S49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="T49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U49" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="V49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="X49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z49" s="12" t="s">
         <x:v>46</x:v>
@@ -6440,10 +6452,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AB49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="s">
         <x:v>46</x:v>
@@ -6452,22 +6464,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AF49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AH49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AJ49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
         <x:v>46</x:v>
@@ -6476,39 +6488,39 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AN49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ49" s="12">
-        <x:v>12</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="AS49" s="12">
-        <x:v>27</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:46">
       <x:c r="A50" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E50" s="12" t="s">
         <x:v>46</x:v>
@@ -6520,7 +6532,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="H50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I50" s="12" t="s">
         <x:v>46</x:v>
@@ -6532,7 +6544,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="L50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M50" s="12" t="s">
         <x:v>46</x:v>
@@ -6544,7 +6556,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="P50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q50" s="12" t="s">
         <x:v>46</x:v>
@@ -6556,19 +6568,19 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="T50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="X50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y50" s="12" t="s">
         <x:v>46</x:v>
@@ -6580,7 +6592,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AB50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="s">
         <x:v>46</x:v>
@@ -6592,19 +6604,19 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AF50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="AJ50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK50" s="12" t="s">
         <x:v>46</x:v>
@@ -6616,30 +6628,30 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AN50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ50" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AR50" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS50" s="12">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AT50" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:46">
       <x:c r="A51" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
         <x:v>43</x:v>
@@ -6660,10 +6672,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H51" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I51" s="12" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="I51" s="12" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="J51" s="12" t="s">
         <x:v>46</x:v>
@@ -6672,10 +6684,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="L51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N51" s="12" t="s">
         <x:v>46</x:v>
@@ -6684,34 +6696,34 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="P51" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q51" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R51" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="T51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U51" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="V51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="X51" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y51" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z51" s="12" t="s">
         <x:v>46</x:v>
@@ -6723,7 +6735,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD51" s="12" t="s">
         <x:v>46</x:v>
@@ -6732,22 +6744,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AF51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG51" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="AH51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="AJ51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
         <x:v>46</x:v>
@@ -6756,42 +6768,42 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AN51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ51" s="12">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AR51" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AS51" s="12">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="AT51" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:46">
       <x:c r="A52" s="11" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D52" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E52" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F52" s="12" t="s">
         <x:v>46</x:v>
@@ -6800,10 +6812,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I52" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J52" s="12" t="s">
         <x:v>46</x:v>
@@ -6812,10 +6824,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="L52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N52" s="12" t="s">
         <x:v>46</x:v>
@@ -6824,34 +6836,34 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="P52" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q52" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="T52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="X52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z52" s="12" t="s">
         <x:v>46</x:v>
@@ -6860,10 +6872,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AB52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD52" s="12" t="s">
         <x:v>46</x:v>
@@ -6872,22 +6884,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AF52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="AJ52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL52" s="12" t="s">
         <x:v>46</x:v>
@@ -6896,30 +6908,30 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AN52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ52" s="12">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR52" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS52" s="12">
-        <x:v>85</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="AT52" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:46">
       <x:c r="A53" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B53" s="12" t="s">
         <x:v>43</x:v>
@@ -6928,10 +6940,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D53" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E53" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F53" s="12" t="s">
         <x:v>46</x:v>
@@ -6943,7 +6955,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="I53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J53" s="12" t="s">
         <x:v>46</x:v>
@@ -6955,7 +6967,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N53" s="12" t="s">
         <x:v>46</x:v>
@@ -6964,25 +6976,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="P53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="T53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W53" s="12">
         <x:v>41</x:v>
@@ -6991,7 +7003,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="Y53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z53" s="12" t="s">
         <x:v>46</x:v>
@@ -7000,10 +7012,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AB53" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD53" s="12" t="s">
         <x:v>46</x:v>
@@ -7012,22 +7024,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AF53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="AJ53" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL53" s="12" t="s">
         <x:v>46</x:v>
@@ -7036,33 +7048,33 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AN53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ53" s="12">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AS53" s="12">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AT53" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:46">
       <x:c r="A54" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B54" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C54" s="12">
         <x:v>42</x:v>
@@ -7071,7 +7083,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F54" s="12" t="s">
         <x:v>46</x:v>
@@ -7080,10 +7092,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I54" s="12" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="I54" s="12" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="J54" s="12" t="s">
         <x:v>46</x:v>
@@ -7092,10 +7104,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M54" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N54" s="12" t="s">
         <x:v>46</x:v>
@@ -7104,34 +7116,34 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="P54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Q54" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R54" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="T54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="X54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y54" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z54" s="12" t="s">
         <x:v>46</x:v>
@@ -7140,10 +7152,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="s">
         <x:v>46</x:v>
@@ -7152,22 +7164,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AF54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="AH54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
         <x:v>46</x:v>
@@ -7176,30 +7188,30 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AN54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ54" s="12">
-        <x:v>0</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="AS54" s="12">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AT54" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:46">
       <x:c r="A55" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
         <x:v>43</x:v>
@@ -7208,10 +7220,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E55" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F55" s="12" t="s">
         <x:v>46</x:v>
@@ -7223,7 +7235,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="I55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J55" s="12" t="s">
         <x:v>46</x:v>
@@ -7232,10 +7244,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L55" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M55" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N55" s="12" t="s">
         <x:v>46</x:v>
@@ -7244,31 +7256,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="P55" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q55" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R55" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="S55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="T55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="X55" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Y55" s="12" t="s">
         <x:v>47</x:v>
@@ -7280,10 +7292,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB55" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AD55" s="12" t="s">
         <x:v>46</x:v>
@@ -7292,22 +7304,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AF55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="AJ55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
         <x:v>46</x:v>
@@ -7316,42 +7328,42 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AN55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ55" s="12">
-        <x:v>72</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AR55" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS55" s="12">
-        <x:v>60</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AT55" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:46">
       <x:c r="A56" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B56" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F56" s="12" t="s">
         <x:v>46</x:v>
@@ -7360,10 +7372,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I56" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J56" s="12" t="s">
         <x:v>46</x:v>
@@ -7372,10 +7384,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="L56" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M56" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N56" s="12" t="s">
         <x:v>46</x:v>
@@ -7387,31 +7399,31 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Q56" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R56" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="T56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="X56" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z56" s="12" t="s">
         <x:v>46</x:v>
@@ -7420,10 +7432,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD56" s="12" t="s">
         <x:v>46</x:v>
@@ -7432,22 +7444,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AF56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL56" s="12" t="s">
         <x:v>46</x:v>
@@ -7456,90 +7468,90 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AN56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ56" s="12">
-        <x:v>80</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS56" s="12">
-        <x:v>68</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="AT56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:46">
       <x:c r="A57" s="13" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B57" s="13" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C57" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D57" s="7"/>
       <x:c r="E57" s="7"/>
       <x:c r="F57" s="7"/>
       <x:c r="G57" s="7" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H57" s="7"/>
       <x:c r="I57" s="7"/>
       <x:c r="J57" s="7"/>
       <x:c r="K57" s="7" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="L57" s="7"/>
       <x:c r="M57" s="7"/>
       <x:c r="N57" s="7"/>
       <x:c r="O57" s="7" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="P57" s="7"/>
       <x:c r="Q57" s="7"/>
       <x:c r="R57" s="7"/>
       <x:c r="S57" s="7" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="T57" s="7"/>
       <x:c r="U57" s="7"/>
       <x:c r="V57" s="7"/>
       <x:c r="W57" s="7" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="X57" s="7"/>
       <x:c r="Y57" s="7"/>
       <x:c r="Z57" s="7"/>
       <x:c r="AA57" s="7" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="AB57" s="7"/>
       <x:c r="AC57" s="7"/>
       <x:c r="AD57" s="7"/>
       <x:c r="AE57" s="7" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="AF57" s="7"/>
       <x:c r="AG57" s="7"/>
       <x:c r="AH57" s="7"/>
       <x:c r="AI57" s="7" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="AJ57" s="7"/>
       <x:c r="AK57" s="7"/>
       <x:c r="AL57" s="7"/>
       <x:c r="AM57" s="7" t="s">
-        <x:v>144</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="AN57" s="7"/>
       <x:c r="AO57" s="7"/>
@@ -7551,37 +7563,37 @@
     </x:row>
     <x:row r="59" spans="1:46">
       <x:c r="A59" s="14" t="s">
-        <x:v>146</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:46">
       <x:c r="A60" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:46">
       <x:c r="A61" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:46">
       <x:c r="A62" s="13" t="s">
-        <x:v>149</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:46">
       <x:c r="A63" s="13" t="s">
-        <x:v>150</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:46">
       <x:c r="A64" s="13" t="s">
-        <x:v>151</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:46">
       <x:c r="A65" s="13" t="s">
-        <x:v>152</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
